--- a/docs/Weapons.xlsx
+++ b/docs/Weapons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8274556-C3FC-4559-9B5C-8DC1746B56BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87A5261-A26A-475F-8A41-C7E2602C900F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{E565F22D-58E8-40F1-A69B-9A398A2EE1F4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Weapon</t>
   </si>
@@ -92,7 +92,19 @@
     <t>Ak47</t>
   </si>
   <si>
-    <t>n/a</t>
+    <t>Calibre</t>
+  </si>
+  <si>
+    <t>9mm</t>
+  </si>
+  <si>
+    <t>5.56mm</t>
+  </si>
+  <si>
+    <t>7.62x39mm</t>
+  </si>
+  <si>
+    <t>Muzzle velocity (m/s)</t>
   </si>
 </sst>
 </file>
@@ -486,14 +498,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF433A9-8029-4CAF-A97A-E25755C0BEEB}">
-  <dimension ref="B3:M6"/>
+  <dimension ref="B3:O6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="13" width="15.59765625" customWidth="1"/>
+    <col min="2" max="15" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" ht="57" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:15" ht="57" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,8 +542,14 @@
       <c r="M3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="N3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
@@ -560,8 +578,8 @@
       <c r="J4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>17</v>
+      <c r="K4" s="3">
+        <v>180</v>
       </c>
       <c r="L4" s="3">
         <v>15</v>
@@ -569,8 +587,15 @@
       <c r="M4" s="3">
         <v>15</v>
       </c>
+      <c r="N4" s="3">
+        <f>374/2</f>
+        <v>187</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
@@ -608,8 +633,15 @@
       <c r="M5" s="3">
         <v>20</v>
       </c>
+      <c r="N5" s="3">
+        <f>910/2</f>
+        <v>455</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
@@ -646,6 +678,13 @@
       </c>
       <c r="M6" s="3">
         <v>25</v>
+      </c>
+      <c r="N6" s="3">
+        <f>712/2</f>
+        <v>356</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Weapons.xlsx
+++ b/docs/Weapons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87A5261-A26A-475F-8A41-C7E2602C900F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB79546-E797-4CD2-B8F3-26F644247D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{E565F22D-58E8-40F1-A69B-9A398A2EE1F4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Weapon</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>Muzzle velocity (m/s)</t>
+  </si>
+  <si>
+    <t>RPG-7</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>40mm</t>
   </si>
 </sst>
 </file>
@@ -498,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF433A9-8029-4CAF-A97A-E25755C0BEEB}">
-  <dimension ref="B3:O6"/>
+  <dimension ref="B3:O7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -687,6 +696,50 @@
         <v>20</v>
       </c>
     </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>80</v>
+      </c>
+      <c r="G7" s="3">
+        <v>100</v>
+      </c>
+      <c r="H7" s="3">
+        <v>100</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="3">
+        <v>30</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>115</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Weapons.xlsx
+++ b/docs/Weapons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Warehouse-7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB79546-E797-4CD2-B8F3-26F644247D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC708D05-B59A-4219-BE56-424AA4E53857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{E565F22D-58E8-40F1-A69B-9A398A2EE1F4}"/>
   </bookViews>
@@ -591,7 +591,7 @@
         <v>180</v>
       </c>
       <c r="L4" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M4" s="3">
         <v>15</v>
@@ -719,7 +719,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
